--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T23:02:46+00:00</t>
+    <t>2026-07-23T04:49:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T04:49:55+00:00</t>
+    <t>2026-07-23T04:55:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -30,7 +30,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/modul-demo/StructureDefinition/example-patient</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/modul-template/StructureDefinition/example-patient</t>
   </si>
   <si>
     <t>Version</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T04:55:59+00:00</t>
+    <t>2026-07-23T09:11:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T09:11:57+00:00</t>
+    <t>2026-07-23T11:08:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T11:08:48+00:00</t>
+    <t>2026-07-23T11:42:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T11:42:24+00:00</t>
+    <t>2026-07-23T22:17:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T22:17:20+00:00</t>
+    <t>2026-07-23T22:34:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T22:34:56+00:00</t>
+    <t>2026-07-23T23:27:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T23:27:01+00:00</t>
+    <t>2026-07-23T23:35:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T23:35:30+00:00</t>
+    <t>2026-07-23T23:38:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T23:38:47+00:00</t>
+    <t>2026-07-23T23:49:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T23:49:49+00:00</t>
+    <t>2026-07-25T22:17:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-25T22:17:48+00:00</t>
+    <t>2026-07-25T22:20:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-25T22:20:51+00:00</t>
+    <t>2026-07-25T22:28:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-25T22:28:53+00:00</t>
+    <t>2026-07-26T07:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T07:03:00+00:00</t>
+    <t>2026-07-26T07:52:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T07:52:05+00:00</t>
+    <t>2026-07-26T09:08:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T09:08:18+00:00</t>
+    <t>2026-07-26T10:07:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T10:07:24+00:00</t>
+    <t>2026-07-26T10:42:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T10:42:02+00:00</t>
+    <t>2026-07-26T10:49:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1906" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1907" uniqueCount="350">
   <si>
     <t>Property</t>
   </si>
@@ -48,7 +48,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Beispiel-Patient (Vorlage)</t>
+    <t>Example Patient — template starter</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,10 +60,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T10:49:04+00:00</t>
+    <t>2026-07-26T11:56:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +90,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Minimales Beispielprofil, das nur mit der Vorlage ausgeliefert wird, damit ein neu erstelltes Modul sofort eine gerenderte IG erzeugt. Kein MII-Artefakt — ersetzen Sie es durch die Profile Ihres Moduls.</t>
+    <t>Minimal example profile shipped with the template so that a newly created module renders a complete IG immediately. Not an MII artifact — replace it with your module's profiles.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -117,13 +120,10 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Patient|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Patient</t>
   </si>
   <si>
     <t>Abstract</t>
-  </si>
-  <si>
-    <t>false</t>
   </si>
   <si>
     <t>Derivation</t>
@@ -1313,98 +1313,100 @@
       <c r="A8" t="s" s="2">
         <v>14</v>
       </c>
-      <c r="B8" s="2"/>
+      <c r="B8" t="s" s="2">
+        <v>15</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -1580,10 +1582,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" t="s" s="2">
@@ -1663,7 +1665,7 @@
         <v>78</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AH2" t="s" s="2">
         <v>76</v>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T11:56:12+00:00</t>
+    <t>2026-07-26T12:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T12:24:24+00:00</t>
+    <t>2026-07-26T13:08:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T13:08:25+00:00</t>
+    <t>2026-07-26T14:56:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T14:56:41+00:00</t>
+    <t>2026-07-26T18:22:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T18:22:37+00:00</t>
+    <t>2026-07-26T18:54:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T18:54:16+00:00</t>
+    <t>2026-07-27T01:54:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T01:54:23+00:00</t>
+    <t>2026-07-27T07:41:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T07:41:45+00:00</t>
+    <t>2026-07-27T08:02:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T08:02:41+00:00</t>
+    <t>2026-07-27T10:33:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T10:33:27+00:00</t>
+    <t>2026-07-27T11:05:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T11:05:36+00:00</t>
+    <t>2026-07-29T19:15:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T19:15:40+00:00</t>
+    <t>2026-07-29T19:27:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T19:27:30+00:00</t>
+    <t>2026-07-29T19:30:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T19:30:52+00:00</t>
+    <t>2026-07-30T03:36:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T03:36:06+00:00</t>
+    <t>2026-07-30T09:43:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T09:43:11+00:00</t>
+    <t>2026-07-30T10:04:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.0.0</t>
+    <t>2027.0.0-draft.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T10:04:49+00:00</t>
+    <t>2026-07-30T13:14:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T13:14:56+00:00</t>
+    <t>2026-07-30T14:06:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:06:53+00:00</t>
+    <t>2026-07-30T15:06:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T15:06:42+00:00</t>
+    <t>2026-07-30T15:25:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T15:25:23+00:00</t>
+    <t>2026-07-30T15:42:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T15:42:59+00:00</t>
+    <t>2026-07-30T16:08:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Medical Informatics Initiative (MII) (https://www.medizininformatik-initiative.de/en)</t>
+    <t>Medical Informatics Initiative (MII) (https://www.medizininformatik-initiative.de)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T16:08:08+00:00</t>
+    <t>2026-07-30T16:22:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T16:22:12+00:00</t>
+    <t>2026-07-30T19:07:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T19:07:27+00:00</t>
+    <t>2026-07-30T19:37:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T19:37:52+00:00</t>
+    <t>2026-07-30T19:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T19:57:28+00:00</t>
+    <t>2026-08-05T20:55:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T20:55:50+00:00</t>
+    <t>2026-08-06T08:02:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T08:02:53+00:00</t>
+    <t>2026-08-06T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T08:08:15+00:00</t>
+    <t>2026-08-06T10:03:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T10:03:43+00:00</t>
+    <t>2026-08-06T10:09:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T10:09:12+00:00</t>
+    <t>2026-08-06T11:57:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T11:57:49+00:00</t>
+    <t>2026-08-06T14:27:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T14:27:12+00:00</t>
+    <t>2026-08-07T05:30:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T05:30:46+00:00</t>
+    <t>2026-08-07T06:35:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T06:35:44+00:00</t>
+    <t>2026-08-07T06:45:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T06:45:20+00:00</t>
+    <t>2026-08-07T06:51:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T06:51:45+00:00</t>
+    <t>2026-08-13T13:00:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T13:00:52+00:00</t>
+    <t>2026-08-13T19:18:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T19:18:57+00:00</t>
+    <t>2026-08-13T19:24:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T19:24:01+00:00</t>
+    <t>2026-08-13T19:50:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T19:50:14+00:00</t>
+    <t>2026-08-14T02:40:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T02:40:11+00:00</t>
+    <t>2026-08-14T02:52:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T02:52:56+00:00</t>
+    <t>2026-08-14T02:58:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T02:58:31+00:00</t>
+    <t>2026-08-14T05:24:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T05:24:37+00:00</t>
+    <t>2026-08-14T05:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T05:30:16+00:00</t>
+    <t>2026-08-14T05:35:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,19 +66,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T05:35:38+00:00</t>
+    <t>2026-08-14T08:34:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Medical Informatics Initiative (MII)</t>
+    <t>NUM-DIZ</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>Medical Informatics Initiative (MII) (https://www.medizininformatik-initiative.de)</t>
+    <t>NUM-DIZ (https://www.netzwerk-universitaetsmedizin.de)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T08:34:32+00:00</t>
+    <t>2026-08-14T08:42:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T08:42:37+00:00</t>
+    <t>2026-08-14T09:44:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T09:44:03+00:00</t>
+    <t>2026-08-14T09:53:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T09:53:11+00:00</t>
+    <t>2026-08-14T10:20:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T10:20:18+00:00</t>
+    <t>2026-08-14T10:36:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T10:36:36+00:00</t>
+    <t>2026-08-14T11:08:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T11:08:59+00:00</t>
+    <t>2026-08-14T11:23:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T11:23:15+00:00</t>
+    <t>2026-08-14T12:02:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:02:27+00:00</t>
+    <t>2026-08-14T12:17:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:17:03+00:00</t>
+    <t>2026-08-14T12:32:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:32:09+00:00</t>
+    <t>2026-08-14T12:46:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:46:33+00:00</t>
+    <t>2026-08-15T07:35:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-15T07:35:20+00:00</t>
+    <t>2026-08-15T21:56:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-15T21:56:20+00:00</t>
+    <t>2026-08-16T07:31:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-16T07:31:50+00:00</t>
+    <t>2026-08-16T09:16:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-16T09:16:40+00:00</t>
+    <t>2026-08-16T09:39:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-16T09:39:12+00:00</t>
+    <t>2026-08-16T10:07:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-16T10:07:45+00:00</t>
+    <t>2026-08-16T11:24:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-16T11:24:31+00:00</t>
+    <t>2026-08-16T11:52:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-16T11:52:19+00:00</t>
+    <t>2026-08-16T12:06:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-16T12:06:55+00:00</t>
+    <t>2026-08-16T12:35:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-16T12:35:03+00:00</t>
+    <t>2026-08-16T12:43:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-16T12:43:03+00:00</t>
+    <t>2026-08-16T14:05:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-16T14:05:10+00:00</t>
+    <t>2026-08-17T19:54:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T19:54:54+00:00</t>
+    <t>2026-08-17T20:00:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T20:00:21+00:00</t>
+    <t>2026-08-17T20:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T20:05:21+00:00</t>
+    <t>2026-08-18T12:38:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T12:38:44+00:00</t>
+    <t>2026-08-18T19:06:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T19:06:13+00:00</t>
+    <t>2026-08-19T15:28:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T15:28:33+00:00</t>
+    <t>2026-08-19T17:39:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T17:39:45+00:00</t>
+    <t>2026-08-19T20:24:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T20:24:56+00:00</t>
+    <t>2026-08-20T09:57:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/all-profiles.xlsx
+++ b/branches/dev/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T09:57:13+00:00</t>
+    <t>2026-08-20T10:04:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
